--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>126097949469 $\pm$ 5599135398</t>
+          <t>613457758794 $\pm$ 3207538001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111442361129 $\pm$ 6489275657</t>
+          <t>553653601740 $\pm$ 4253940560</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>99211826774 $\pm$ 5008231589</t>
+          <t>495873467847 $\pm$ 3374417934</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>85652192032 $\pm$ 4706298627</t>
+          <t>432605102061 $\pm$ 2661304876</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>541632808959 $\pm$ 4252484004</t>
+          <t>614550589246 $\pm$ 3829250792</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>474017026759 $\pm$ 5524736995</t>
+          <t>552457593235 $\pm$ 4741244927</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>412973023963 $\pm$ 3675382710</t>
+          <t>494733428903 $\pm$ 3517588370</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>353327252448 $\pm$ 4286103724</t>
+          <t>434933680908 $\pm$ 4873485422</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>613457758794 $\pm$ 3207538001</t>
+          <t>126097949469 $\pm$ 5599135398</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>553653601740 $\pm$ 4253940560</t>
+          <t>111442361129 $\pm$ 6489275657</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>495873467847 $\pm$ 3374417934</t>
+          <t>99211826774 $\pm$ 5008231589</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>432605102061 $\pm$ 2661304876</t>
+          <t>85652192032 $\pm$ 4706298627</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>614550589246 $\pm$ 3829250792</t>
+          <t>541632808959 $\pm$ 4252484004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>552457593235 $\pm$ 4741244927</t>
+          <t>474017026759 $\pm$ 5524736995</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>494733428903 $\pm$ 3517588370</t>
+          <t>412973023963 $\pm$ 3675382710</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>434933680908 $\pm$ 4873485422</t>
+          <t>353327252448 $\pm$ 4286103724</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>652905472191 $\pm$ 3795613014</t>
+          <t>618251411900 $\pm$ 1635671646</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>625215658756 $\pm$ 2571515299</t>
+          <t>560449136691 $\pm$ 2629501058</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>599013157425 $\pm$ 4287981888</t>
+          <t>503822792142 $\pm$ 3388233163</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>571928448843 $\pm$ 5962103633</t>
+          <t>448246602617 $\pm$ 3767477155</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85902423780 $\pm$ 7503268278</t>
+          <t>85035090500 $\pm$ 237538674</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79794037560 $\pm$ 5759149991</t>
+          <t>77758961237 $\pm$ 182496366</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>74004982839 $\pm$ 7248881089</t>
+          <t>70896413785 $\pm$ 229411031</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66116412986 $\pm$ 6221164858</t>
+          <t>64375230958 $\pm$ 196728515</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>126097949469 $\pm$ 5599135398</t>
+          <t>111162466311 $\pm$ 1514598367</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111442361129 $\pm$ 6489275657</t>
+          <t>97967355550 $\pm$ 1107309184</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>99211826774 $\pm$ 5008231589</t>
+          <t>85844124129 $\pm$ 1719108614</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>85652192032 $\pm$ 4706298627</t>
+          <t>72355313726 $\pm$ 1487809155</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>541632808959 $\pm$ 4252484004</t>
+          <t>203984442314 $\pm$ 7216682775</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>474017026759 $\pm$ 5524736995</t>
+          <t>167956191740 $\pm$ 5236006687</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>412973023963 $\pm$ 3675382710</t>
+          <t>134883303314 $\pm$ 8478914306</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>353327252448 $\pm$ 4286103724</t>
+          <t>93022810478 $\pm$ 8070299844</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AGM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-215789421540 $\pm$ 999602121696</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-1184297763397 $\pm$ 3317469030083</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-5341467434809 $\pm$ 14424516229194</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-1377050782057 $\pm$ 3514342444889</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>111162466311 $\pm$ 1514598367</t>
+          <t>118313395016 $\pm$ 867566985</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>97967355550 $\pm$ 1107309184</t>
+          <t>104466540145 $\pm$ 645281801</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>85844124129 $\pm$ 1719108614</t>
+          <t>91690507635 $\pm$ 993368768</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72355313726 $\pm$ 1487809155</t>
+          <t>78509390697 $\pm$ 835770396</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>203984442314 $\pm$ 7216682775</t>
+          <t>235378270288 $\pm$ 4187677120</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>167956191740 $\pm$ 5236006687</t>
+          <t>197475481461 $\pm$ 2969661817</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>134883303314 $\pm$ 8478914306</t>
+          <t>162490825267 $\pm$ 4876880178</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>93022810478 $\pm$ 8070299844</t>
+          <t>123608760492 $\pm$ 4656565976</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-215789421540 $\pm$ 999602121696</t>
+          <t>159323190515 $\pm$ 284340602825</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1184297763397 $\pm$ 3317469030083</t>
+          <t>310759377382 $\pm$ 131386077906</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-5341467434809 $\pm$ 14424516229194</t>
+          <t>71846217891 $\pm$ 186332867822</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1377050782057 $\pm$ 3514342444889</t>
+          <t>202309793799 $\pm$ 185242187655</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,22 +571,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>159323190515 $\pm$ 284340602825</t>
+          <t>433208230449 $\pm$ 105572359726</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>310759377382 $\pm$ 131386077906</t>
+          <t>449949559027 $\pm$ 93492000718</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>71846217891 $\pm$ 186332867822</t>
+          <t>275710029581 $\pm$ 147699664386</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>202309793799 $\pm$ 185242187655</t>
+          <t>234503382649 $\pm$ 190568312791</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>OPGD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>297212091100 $\pm$ 54457366832</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>233505327608 $\pm$ 75972292809</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>181244146006 $\pm$ 60056530193</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85106284879 $\pm$ 77867494204</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>297212091100 $\pm$ 54457366832</t>
+          <t>361785347443 $\pm$ 68669589294</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>233505327608 $\pm$ 75972292809</t>
+          <t>355973349480 $\pm$ 36688804447</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>181244146006 $\pm$ 60056530193</t>
+          <t>281432972894 $\pm$ 89134716146</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>85106284879 $\pm$ 77867494204</t>
+          <t>208427770814 $\pm$ 69948415659</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,49 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>433208230449 $\pm$ 105572359726</t>
+          <t>433459478716 $\pm$ 105348939269</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>449949559027 $\pm$ 93492000718</t>
+          <t>449946660353 $\pm$ 93499995514</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>275710029581 $\pm$ 147699664386</t>
+          <t>275708975998 $\pm$ 147699583764</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>234503382649 $\pm$ 190568312791</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>OPGD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>361785347443 $\pm$ 68669589294</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>355973349480 $\pm$ 36688804447</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>281432972894 $\pm$ 89134716146</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>208427770814 $\pm$ 69948415659</t>
+          <t>237023914683 $\pm$ 190200297926</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>$\mu_A$ = 0.25</t>
+          <t>$\mu$ = 0.25</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>$\mu_A$ = 0.5</t>
+          <t>$\mu$ = 0.5</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>$\mu_A$ = 0.75</t>
+          <t>$\mu$ = 0.75</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>$\mu_A$ = 1.0</t>
+          <t>$\mu$ = 1.0</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,33 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>237023914683 $\pm$ 190200297926</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>OPGD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>361785347443 $\pm$ 68669589294</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>355973349480 $\pm$ 36688804447</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281432972894 $\pm$ 89134716146</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>208427770814 $\pm$ 69948415659</t>
         </is>
       </c>
     </row>

--- a/CournotCompetition/figs/total_revenue.xlsx
+++ b/CournotCompetition/figs/total_revenue.xlsx
@@ -1,43 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\phd\05_multiplayer_performative_stable\multiplayer-performative-stable\CournotCompetition\figs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFF794A-D941-4B5D-8D32-D24F3F4E519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="35">
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>$\mu$ = 0.25</t>
+  </si>
+  <si>
+    <t>$\mu$ = 0.5</t>
+  </si>
+  <si>
+    <t>$\mu$ = 0.75</t>
+  </si>
+  <si>
+    <t>$\mu$ = 1.0</t>
+  </si>
+  <si>
+    <t>SIR$^2$</t>
+  </si>
+  <si>
+    <t>618251411923 $\pm$ 1635671644</t>
+  </si>
+  <si>
+    <t>560449136725 $\pm$ 2629501069</t>
+  </si>
+  <si>
+    <t>503822792211 $\pm$ 3388233272</t>
+  </si>
+  <si>
+    <t>448246602633 $\pm$ 3767477132</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>85035090500 $\pm$ 237538674</t>
+  </si>
+  <si>
+    <t>77758961237 $\pm$ 182496366</t>
+  </si>
+  <si>
+    <t>70896413786 $\pm$ 229411032</t>
+  </si>
+  <si>
+    <t>64375230958 $\pm$ 196728515</t>
+  </si>
+  <si>
+    <t>RGD</t>
+  </si>
+  <si>
+    <t>118313395016 $\pm$ 867566985</t>
+  </si>
+  <si>
+    <t>104466540145 $\pm$ 645281801</t>
+  </si>
+  <si>
+    <t>91690507635 $\pm$ 993368768</t>
+  </si>
+  <si>
+    <t>78509390697 $\pm$ 835770396</t>
+  </si>
+  <si>
+    <t>SFB</t>
+  </si>
+  <si>
+    <t>235378270289 $\pm$ 4187677120</t>
+  </si>
+  <si>
+    <t>197475481462 $\pm$ 2969661817</t>
+  </si>
+  <si>
+    <t>162490825268 $\pm$ 4876880178</t>
+  </si>
+  <si>
+    <t>123608760493 $\pm$ 4656565976</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>433178569023 $\pm$ 105599160581</t>
+  </si>
+  <si>
+    <t>449946235135 $\pm$ 93499995063</t>
+  </si>
+  <si>
+    <t>275705686600 $\pm$ 147704759267</t>
+  </si>
+  <si>
+    <t>234758549675 $\pm$ 190519125599</t>
+  </si>
+  <si>
+    <t>OPGD</t>
+  </si>
+  <si>
+    <t>361785347444 $\pm$ 68669589294</t>
+  </si>
+  <si>
+    <t>355973349481 $\pm$ 36688804447</t>
+  </si>
+  <si>
+    <t>281432972896 $\pm$ 89134716147</t>
+  </si>
+  <si>
+    <t>208427770817 $\pm$ 69948415660</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -46,93 +179,117 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,204 +577,251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="14" width="8.7265625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu$ = 0.25</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu$ = 0.5</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu$ = 0.75</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu$ = 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>SIR$^2$</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>618251411900 $\pm$ 1635671646</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>560449136691 $\pm$ 2629501058</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>503822792142 $\pm$ 3388233163</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>448246602617 $\pm$ 3767477155</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>85035090500 $\pm$ 237538674</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>77758961237 $\pm$ 182496366</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>70896413785 $\pm$ 229411031</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>64375230958 $\pm$ 196728515</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>RGD</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>118313395016 $\pm$ 867566985</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>104466540145 $\pm$ 645281801</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>91690507635 $\pm$ 993368768</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>78509390697 $\pm$ 835770396</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SFB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>235378270288 $\pm$ 4187677120</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>197475481461 $\pm$ 2969661817</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>162490825267 $\pm$ 4876880178</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>123608760492 $\pm$ 4656565976</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>AGM</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>433459478716 $\pm$ 105348939269</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>449946660353 $\pm$ 93499995514</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>275708975998 $\pm$ 147699583764</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>237023914683 $\pm$ 190200297926</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>OPGD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>361785347443 $\pm$ 68669589294</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>355973349480 $\pm$ 36688804447</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>281432972894 $\pm$ 89134716146</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>208427770814 $\pm$ 69948415659</t>
-        </is>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J13" s="5"/>
+      <c r="K13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>